--- a/samples/wildling/기획데이터/Battle.xlsx
+++ b/samples/wildling/기획데이터/Battle.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2249" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="325">
   <si>
     <t xml:space="preserve">:table Skill</t>
   </si>
@@ -625,6 +625,24 @@
     <t xml:space="preserve">이 행의 효과가 어떤 형태인가</t>
   </si>
   <si>
+    <t xml:space="preserve">발동 확률. 만분율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 또는 회복 배수. 만분율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부여하는 상태</t>
+  </si>
+  <si>
+    <t xml:space="preserve">변동시키는 능력치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">변동률. 만분율. 음수는 하락</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지속 턴</t>
+  </si>
+  <si>
     <t xml:space="preserve">DamageEffect</t>
   </si>
   <si>
@@ -697,6 +715,15 @@
     <t xml:space="preserve">소모 재화</t>
   </si>
   <si>
+    <t xml:space="preserve">첫째 소모 수량</t>
+  </si>
+  <si>
+    <t xml:space="preserve">둘째 소모 재화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">둘째 소모 수량</t>
+  </si>
+  <si>
     <t xml:space="preserve">gold</t>
   </si>
   <si>
@@ -850,12 +877,51 @@
     <t xml:space="preserve">계수. 만분율</t>
   </si>
   <si>
+    <t xml:space="preserve">공격 계수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방어 계수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">행동 순서 계수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 확률 계수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 배수 계수</t>
+  </si>
+  <si>
     <t xml:space="preserve">특수 능력</t>
   </si>
   <si>
     <t xml:space="preserve">페이즈별 행동 순서</t>
   </si>
   <si>
+    <t xml:space="preserve">1페이즈 2번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1페이즈 3번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2페이즈 1번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2페이즈 2번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2페이즈 3번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3페이즈 1번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3페이즈 2번째 행동</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3페이즈 3번째 행동</t>
+  </si>
+  <si>
     <t xml:space="preserve">등장 연출의 회전</t>
   </si>
   <si>
@@ -863,6 +929,12 @@
   </si>
   <si>
     <t xml:space="preserve">특수 능력의 효과. 원소가 행에서 온다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 또는 회복 배수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">변동률. 만분율</t>
   </si>
   <si>
     <t xml:space="preserve">boss_weir_forest</t>
@@ -2346,10 +2418,10 @@
     <col min="3" max="3" width="23.4375" customWidth="1"/>
     <col min="4" max="4" width="21.09375" customWidth="1"/>
     <col min="5" max="5" width="17.578125" customWidth="1"/>
-    <col min="6" max="6" width="16.40625" customWidth="1"/>
+    <col min="6" max="6" width="21.09375" customWidth="1"/>
     <col min="7" max="7" width="17.578125" customWidth="1"/>
     <col min="8" max="8" width="15.234375" customWidth="1"/>
-    <col min="9" max="9" width="16.40625" customWidth="1"/>
+    <col min="9" max="9" width="21.09375" customWidth="1"/>
     <col min="10" max="10" width="19.921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2434,12 +2506,24 @@
       <c r="D4" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -2454,12 +2538,24 @@
       <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
@@ -2469,25 +2565,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E6" s="6">
         <v>10000</v>
       </c>
       <c r="F6" s="6">
         <v>18000</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7">
@@ -2498,25 +2582,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E7" s="7">
         <v>10000</v>
       </c>
       <c r="F7" s="7">
         <v>26000</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="8">
@@ -2527,25 +2599,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E8" s="6">
         <v>10000</v>
       </c>
       <c r="F8" s="6">
         <v>11000</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="9">
@@ -2556,22 +2616,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E9" s="7">
         <v>2500</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -2585,19 +2636,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E10" s="6">
         <v>10000</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H10" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I10" s="6">
         <v>3000</v>
@@ -2614,25 +2659,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E11" s="7">
         <v>10000</v>
       </c>
       <c r="F11" s="7">
         <v>14000</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -2643,22 +2676,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E12" s="6">
         <v>6000</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="J12" s="6">
         <v>2</v>
@@ -2672,19 +2696,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E13" s="7">
         <v>10000</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H13" s="7" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I13" s="7">
         <v>2500</v>
@@ -2701,25 +2719,13 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E14" s="6">
         <v>10000</v>
       </c>
       <c r="F14" s="6">
         <v>18000</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="15">
@@ -2730,22 +2736,13 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E15" s="7">
         <v>4000</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G15" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="J15" s="7">
         <v>2</v>
@@ -2759,19 +2756,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E16" s="6">
         <v>10000</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I16" s="6">
         <v>-1500</v>
@@ -2788,19 +2779,13 @@
         <v>0</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E17" s="7">
         <v>10000</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H17" s="7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I17" s="7">
         <v>3000</v>
@@ -2817,25 +2802,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E18" s="6">
         <v>10000</v>
       </c>
       <c r="F18" s="6">
         <v>18000</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -2846,25 +2819,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E19" s="7">
         <v>10000</v>
       </c>
       <c r="F19" s="7">
         <v>26000</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="20">
@@ -2875,25 +2836,13 @@
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E20" s="6">
         <v>10000</v>
       </c>
       <c r="F20" s="6">
         <v>11000</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="21">
@@ -2904,22 +2853,13 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E21" s="7">
         <v>2500</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G21" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2933,19 +2873,13 @@
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E22" s="6">
         <v>10000</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H22" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I22" s="6">
         <v>3000</v>
@@ -2962,25 +2896,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E23" s="7">
         <v>10000</v>
       </c>
       <c r="F23" s="7">
         <v>14000</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="24">
@@ -2991,22 +2913,13 @@
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E24" s="6">
         <v>6000</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="J24" s="6">
         <v>2</v>
@@ -3020,19 +2933,13 @@
         <v>0</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E25" s="7">
         <v>10000</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I25" s="7">
         <v>2500</v>
@@ -3049,25 +2956,13 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E26" s="6">
         <v>10000</v>
       </c>
       <c r="F26" s="6">
         <v>18000</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="27">
@@ -3078,22 +2973,13 @@
         <v>0</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E27" s="7">
         <v>4000</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
@@ -3107,19 +2993,13 @@
         <v>1</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E28" s="6">
         <v>10000</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H28" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I28" s="6">
         <v>-1500</v>
@@ -3136,25 +3016,13 @@
         <v>0</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E29" s="7">
         <v>10000</v>
       </c>
       <c r="F29" s="7">
         <v>18000</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="30">
@@ -3165,25 +3033,13 @@
         <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E30" s="6">
         <v>10000</v>
       </c>
       <c r="F30" s="6">
         <v>26000</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="31">
@@ -3194,25 +3050,13 @@
         <v>0</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E31" s="7">
         <v>10000</v>
       </c>
       <c r="F31" s="7">
         <v>11000</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="32">
@@ -3223,22 +3067,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E32" s="6">
         <v>2500</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G32" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="J32" s="6">
         <v>1</v>
@@ -3252,19 +3087,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E33" s="7">
         <v>10000</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H33" s="7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I33" s="7">
         <v>3000</v>
@@ -3281,25 +3110,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E34" s="6">
         <v>10000</v>
       </c>
       <c r="F34" s="6">
         <v>14000</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="35">
@@ -3310,22 +3127,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E35" s="7">
         <v>6000</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G35" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="J35" s="7">
         <v>2</v>
@@ -3339,19 +3147,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E36" s="6">
         <v>10000</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H36" s="6" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I36" s="6">
         <v>2500</v>
@@ -3368,25 +3170,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E37" s="7">
         <v>10000</v>
       </c>
       <c r="F37" s="7">
         <v>18000</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="38">
@@ -3397,22 +3187,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E38" s="6">
         <v>4000</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G38" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="J38" s="6">
         <v>2</v>
@@ -3426,19 +3207,13 @@
         <v>1</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E39" s="7">
         <v>10000</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H39" s="7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I39" s="7">
         <v>-1500</v>
@@ -3455,19 +3230,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E40" s="6">
         <v>10000</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H40" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I40" s="6">
         <v>3000</v>
@@ -3484,25 +3253,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E41" s="7">
         <v>10000</v>
       </c>
       <c r="F41" s="7">
         <v>18000</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="42">
@@ -3513,25 +3270,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E42" s="6">
         <v>10000</v>
       </c>
       <c r="F42" s="6">
         <v>26000</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="43">
@@ -3542,25 +3287,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E43" s="7">
         <v>10000</v>
       </c>
       <c r="F43" s="7">
         <v>11000</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="44">
@@ -3571,22 +3304,13 @@
         <v>1</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E44" s="6">
         <v>2500</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G44" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="J44" s="6">
         <v>1</v>
@@ -3600,19 +3324,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E45" s="7">
         <v>10000</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H45" s="7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I45" s="7">
         <v>3000</v>
@@ -3629,25 +3347,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E46" s="6">
         <v>10000</v>
       </c>
       <c r="F46" s="6">
         <v>14000</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="47">
@@ -3658,22 +3364,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E47" s="7">
         <v>6000</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G47" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="J47" s="7">
         <v>2</v>
@@ -3687,19 +3384,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E48" s="6">
         <v>10000</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H48" s="6" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I48" s="6">
         <v>2500</v>
@@ -3716,25 +3407,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E49" s="7">
         <v>10000</v>
       </c>
       <c r="F49" s="7">
         <v>18000</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="50">
@@ -3745,22 +3424,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E50" s="6">
         <v>4000</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G50" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="J50" s="6">
         <v>2</v>
@@ -3774,19 +3444,13 @@
         <v>1</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E51" s="7">
         <v>10000</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H51" s="7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I51" s="7">
         <v>-1500</v>
@@ -3803,25 +3467,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E52" s="6">
         <v>10000</v>
       </c>
       <c r="F52" s="6">
         <v>18000</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="53">
@@ -3832,25 +3484,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E53" s="7">
         <v>10000</v>
       </c>
       <c r="F53" s="7">
         <v>26000</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="54">
@@ -3861,25 +3501,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E54" s="6">
         <v>10000</v>
       </c>
       <c r="F54" s="6">
         <v>11000</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="55">
@@ -3890,22 +3518,13 @@
         <v>1</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E55" s="7">
         <v>2500</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="G55" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
@@ -3919,19 +3538,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E56" s="6">
         <v>10000</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H56" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I56" s="6">
         <v>3000</v>
@@ -3948,25 +3561,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E57" s="7">
         <v>10000</v>
       </c>
       <c r="F57" s="7">
         <v>14000</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="58">
@@ -3977,22 +3578,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E58" s="6">
         <v>6000</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="G58" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="J58" s="6">
         <v>2</v>
@@ -4006,19 +3598,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E59" s="7">
         <v>10000</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="H59" s="7" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I59" s="7">
         <v>2500</v>
@@ -4035,19 +3621,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E60" s="6">
         <v>10000</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="H60" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I60" s="6">
         <v>3000</v>
@@ -4079,10 +3659,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4099,22 +3679,22 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
@@ -4125,13 +3705,13 @@
         <v>194</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -4145,17 +3725,23 @@
         <v>197</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+        <v>229</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -4173,9 +3759,15 @@
       <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
@@ -4188,13 +3780,13 @@
         <v>10000</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F6" s="6">
         <v>600</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H6" s="6">
         <v>4</v>
@@ -4211,13 +3803,13 @@
         <v>11200</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F7" s="7">
         <v>2400</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -4234,13 +3826,13 @@
         <v>12400</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F8" s="6">
         <v>5400</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H8" s="6">
         <v>12</v>
@@ -4257,13 +3849,13 @@
         <v>13600</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F9" s="7">
         <v>9600</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H9" s="7">
         <v>16</v>
@@ -4280,13 +3872,13 @@
         <v>14800</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F10" s="6">
         <v>15000</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H10" s="6">
         <v>20</v>
@@ -4303,13 +3895,13 @@
         <v>16000</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F11" s="7">
         <v>21600</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H11" s="7">
         <v>24</v>
@@ -4326,13 +3918,13 @@
         <v>17200</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F12" s="6">
         <v>29400</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H12" s="6">
         <v>28</v>
@@ -4349,13 +3941,13 @@
         <v>18400</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F13" s="7">
         <v>38400</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H13" s="7">
         <v>32</v>
@@ -4372,13 +3964,13 @@
         <v>19600</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F14" s="6">
         <v>48600</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H14" s="6">
         <v>36</v>
@@ -4395,13 +3987,13 @@
         <v>20800</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F15" s="7">
         <v>60000</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H15" s="7">
         <v>40</v>
@@ -4418,13 +4010,13 @@
         <v>10000</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F16" s="6">
         <v>600</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H16" s="6">
         <v>4</v>
@@ -4441,13 +4033,13 @@
         <v>11200</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F17" s="7">
         <v>2400</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H17" s="7">
         <v>8</v>
@@ -4464,13 +4056,13 @@
         <v>12400</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F18" s="6">
         <v>5400</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H18" s="6">
         <v>12</v>
@@ -4487,13 +4079,13 @@
         <v>13600</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F19" s="7">
         <v>9600</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H19" s="7">
         <v>16</v>
@@ -4510,13 +4102,13 @@
         <v>14800</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F20" s="6">
         <v>15000</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H20" s="6">
         <v>20</v>
@@ -4533,13 +4125,13 @@
         <v>16000</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F21" s="7">
         <v>21600</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H21" s="7">
         <v>24</v>
@@ -4556,13 +4148,13 @@
         <v>17200</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F22" s="6">
         <v>29400</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H22" s="6">
         <v>28</v>
@@ -4579,13 +4171,13 @@
         <v>18400</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F23" s="7">
         <v>38400</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H23" s="7">
         <v>32</v>
@@ -4602,13 +4194,13 @@
         <v>19600</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F24" s="6">
         <v>48600</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H24" s="6">
         <v>36</v>
@@ -4625,13 +4217,13 @@
         <v>20800</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F25" s="7">
         <v>60000</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H25" s="7">
         <v>40</v>
@@ -4648,13 +4240,13 @@
         <v>10000</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F26" s="6">
         <v>600</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H26" s="6">
         <v>4</v>
@@ -4671,13 +4263,13 @@
         <v>11200</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F27" s="7">
         <v>2400</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H27" s="7">
         <v>8</v>
@@ -4694,13 +4286,13 @@
         <v>12400</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F28" s="6">
         <v>5400</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H28" s="6">
         <v>12</v>
@@ -4717,13 +4309,13 @@
         <v>13600</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F29" s="7">
         <v>9600</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H29" s="7">
         <v>16</v>
@@ -4740,13 +4332,13 @@
         <v>14800</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F30" s="6">
         <v>15000</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H30" s="6">
         <v>20</v>
@@ -4763,13 +4355,13 @@
         <v>16000</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F31" s="7">
         <v>21600</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H31" s="7">
         <v>24</v>
@@ -4786,13 +4378,13 @@
         <v>17200</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F32" s="6">
         <v>29400</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H32" s="6">
         <v>28</v>
@@ -4809,13 +4401,13 @@
         <v>18400</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F33" s="7">
         <v>38400</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H33" s="7">
         <v>32</v>
@@ -4832,13 +4424,13 @@
         <v>19600</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F34" s="6">
         <v>48600</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H34" s="6">
         <v>36</v>
@@ -4855,13 +4447,13 @@
         <v>20800</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F35" s="7">
         <v>60000</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H35" s="7">
         <v>40</v>
@@ -4878,13 +4470,13 @@
         <v>10000</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F36" s="6">
         <v>600</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H36" s="6">
         <v>4</v>
@@ -4901,13 +4493,13 @@
         <v>11200</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F37" s="7">
         <v>2400</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H37" s="7">
         <v>8</v>
@@ -4924,13 +4516,13 @@
         <v>12400</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F38" s="6">
         <v>5400</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H38" s="6">
         <v>12</v>
@@ -4947,13 +4539,13 @@
         <v>13600</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F39" s="7">
         <v>9600</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H39" s="7">
         <v>16</v>
@@ -4970,13 +4562,13 @@
         <v>14800</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F40" s="6">
         <v>15000</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H40" s="6">
         <v>20</v>
@@ -4993,13 +4585,13 @@
         <v>16000</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F41" s="7">
         <v>21600</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H41" s="7">
         <v>24</v>
@@ -5016,13 +4608,13 @@
         <v>17200</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F42" s="6">
         <v>29400</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H42" s="6">
         <v>28</v>
@@ -5039,13 +4631,13 @@
         <v>18400</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F43" s="7">
         <v>38400</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H43" s="7">
         <v>32</v>
@@ -5062,13 +4654,13 @@
         <v>19600</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F44" s="6">
         <v>48600</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H44" s="6">
         <v>36</v>
@@ -5085,13 +4677,13 @@
         <v>20800</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F45" s="7">
         <v>60000</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H45" s="7">
         <v>40</v>
@@ -5108,13 +4700,13 @@
         <v>10000</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F46" s="6">
         <v>600</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H46" s="6">
         <v>4</v>
@@ -5131,13 +4723,13 @@
         <v>11200</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F47" s="7">
         <v>2400</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H47" s="7">
         <v>8</v>
@@ -5154,13 +4746,13 @@
         <v>12400</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F48" s="6">
         <v>5400</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H48" s="6">
         <v>12</v>
@@ -5177,13 +4769,13 @@
         <v>13600</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F49" s="7">
         <v>9600</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H49" s="7">
         <v>16</v>
@@ -5200,13 +4792,13 @@
         <v>14800</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F50" s="6">
         <v>15000</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H50" s="6">
         <v>20</v>
@@ -5223,13 +4815,13 @@
         <v>16000</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F51" s="7">
         <v>21600</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H51" s="7">
         <v>24</v>
@@ -5246,13 +4838,13 @@
         <v>17200</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F52" s="6">
         <v>29400</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H52" s="6">
         <v>28</v>
@@ -5269,13 +4861,13 @@
         <v>18400</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F53" s="7">
         <v>38400</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H53" s="7">
         <v>32</v>
@@ -5292,13 +4884,13 @@
         <v>19600</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F54" s="6">
         <v>48600</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H54" s="6">
         <v>36</v>
@@ -5315,13 +4907,13 @@
         <v>20800</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F55" s="7">
         <v>60000</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H55" s="7">
         <v>40</v>
@@ -5338,13 +4930,13 @@
         <v>10000</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F56" s="6">
         <v>600</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H56" s="6">
         <v>4</v>
@@ -5361,13 +4953,13 @@
         <v>11200</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F57" s="7">
         <v>2400</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H57" s="7">
         <v>8</v>
@@ -5384,13 +4976,13 @@
         <v>12400</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F58" s="6">
         <v>5400</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H58" s="6">
         <v>12</v>
@@ -5407,13 +4999,13 @@
         <v>13600</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F59" s="7">
         <v>9600</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H59" s="7">
         <v>16</v>
@@ -5430,13 +5022,13 @@
         <v>14800</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F60" s="6">
         <v>15000</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H60" s="6">
         <v>20</v>
@@ -5453,13 +5045,13 @@
         <v>16000</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F61" s="7">
         <v>21600</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H61" s="7">
         <v>24</v>
@@ -5476,13 +5068,13 @@
         <v>17200</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F62" s="6">
         <v>29400</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H62" s="6">
         <v>28</v>
@@ -5499,13 +5091,13 @@
         <v>18400</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F63" s="7">
         <v>38400</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H63" s="7">
         <v>32</v>
@@ -5522,13 +5114,13 @@
         <v>19600</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6">
         <v>48600</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H64" s="6">
         <v>36</v>
@@ -5545,13 +5137,13 @@
         <v>20800</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F65" s="7">
         <v>60000</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H65" s="7">
         <v>40</v>
@@ -5568,13 +5160,13 @@
         <v>10000</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6">
         <v>600</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H66" s="6">
         <v>4</v>
@@ -5591,13 +5183,13 @@
         <v>11200</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F67" s="7">
         <v>2400</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H67" s="7">
         <v>8</v>
@@ -5614,13 +5206,13 @@
         <v>12400</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6">
         <v>5400</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H68" s="6">
         <v>12</v>
@@ -5637,13 +5229,13 @@
         <v>13600</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F69" s="7">
         <v>9600</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H69" s="7">
         <v>16</v>
@@ -5660,13 +5252,13 @@
         <v>14800</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F70" s="6">
         <v>15000</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H70" s="6">
         <v>20</v>
@@ -5683,13 +5275,13 @@
         <v>16000</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F71" s="7">
         <v>21600</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H71" s="7">
         <v>24</v>
@@ -5706,13 +5298,13 @@
         <v>17200</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6">
         <v>29400</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H72" s="6">
         <v>28</v>
@@ -5729,13 +5321,13 @@
         <v>18400</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F73" s="7">
         <v>38400</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H73" s="7">
         <v>32</v>
@@ -5752,13 +5344,13 @@
         <v>19600</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F74" s="6">
         <v>48600</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H74" s="6">
         <v>36</v>
@@ -5775,13 +5367,13 @@
         <v>20800</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F75" s="7">
         <v>60000</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H75" s="7">
         <v>40</v>
@@ -5798,13 +5390,13 @@
         <v>10000</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F76" s="6">
         <v>600</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H76" s="6">
         <v>4</v>
@@ -5821,13 +5413,13 @@
         <v>11200</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F77" s="7">
         <v>2400</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H77" s="7">
         <v>8</v>
@@ -5844,13 +5436,13 @@
         <v>12400</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F78" s="6">
         <v>5400</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H78" s="6">
         <v>12</v>
@@ -5867,13 +5459,13 @@
         <v>13600</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F79" s="7">
         <v>9600</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H79" s="7">
         <v>16</v>
@@ -5890,13 +5482,13 @@
         <v>14800</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F80" s="6">
         <v>15000</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H80" s="6">
         <v>20</v>
@@ -5913,13 +5505,13 @@
         <v>16000</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F81" s="7">
         <v>21600</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H81" s="7">
         <v>24</v>
@@ -5936,13 +5528,13 @@
         <v>17200</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F82" s="6">
         <v>29400</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H82" s="6">
         <v>28</v>
@@ -5959,13 +5551,13 @@
         <v>18400</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F83" s="7">
         <v>38400</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H83" s="7">
         <v>32</v>
@@ -5982,13 +5574,13 @@
         <v>19600</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F84" s="6">
         <v>48600</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H84" s="6">
         <v>36</v>
@@ -6005,13 +5597,13 @@
         <v>20800</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F85" s="7">
         <v>60000</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H85" s="7">
         <v>40</v>
@@ -6028,13 +5620,13 @@
         <v>10000</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F86" s="6">
         <v>600</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H86" s="6">
         <v>4</v>
@@ -6051,13 +5643,13 @@
         <v>11200</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F87" s="7">
         <v>2400</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H87" s="7">
         <v>8</v>
@@ -6074,13 +5666,13 @@
         <v>12400</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F88" s="6">
         <v>5400</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H88" s="6">
         <v>12</v>
@@ -6097,13 +5689,13 @@
         <v>13600</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F89" s="7">
         <v>9600</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H89" s="7">
         <v>16</v>
@@ -6120,13 +5712,13 @@
         <v>14800</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F90" s="6">
         <v>15000</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H90" s="6">
         <v>20</v>
@@ -6143,13 +5735,13 @@
         <v>16000</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F91" s="7">
         <v>21600</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H91" s="7">
         <v>24</v>
@@ -6166,13 +5758,13 @@
         <v>17200</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F92" s="6">
         <v>29400</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H92" s="6">
         <v>28</v>
@@ -6189,13 +5781,13 @@
         <v>18400</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F93" s="7">
         <v>38400</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H93" s="7">
         <v>32</v>
@@ -6212,13 +5804,13 @@
         <v>19600</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F94" s="6">
         <v>48600</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H94" s="6">
         <v>36</v>
@@ -6235,13 +5827,13 @@
         <v>20800</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F95" s="7">
         <v>60000</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H95" s="7">
         <v>40</v>
@@ -6258,13 +5850,13 @@
         <v>10000</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F96" s="6">
         <v>600</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H96" s="6">
         <v>4</v>
@@ -6281,13 +5873,13 @@
         <v>11200</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F97" s="7">
         <v>2400</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H97" s="7">
         <v>8</v>
@@ -6304,13 +5896,13 @@
         <v>12400</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F98" s="6">
         <v>5400</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H98" s="6">
         <v>12</v>
@@ -6327,13 +5919,13 @@
         <v>13600</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F99" s="7">
         <v>9600</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H99" s="7">
         <v>16</v>
@@ -6350,13 +5942,13 @@
         <v>14800</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F100" s="6">
         <v>15000</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H100" s="6">
         <v>20</v>
@@ -6373,13 +5965,13 @@
         <v>16000</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F101" s="7">
         <v>21600</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H101" s="7">
         <v>24</v>
@@ -6396,13 +5988,13 @@
         <v>17200</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F102" s="6">
         <v>29400</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H102" s="6">
         <v>28</v>
@@ -6419,13 +6011,13 @@
         <v>18400</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F103" s="7">
         <v>38400</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H103" s="7">
         <v>32</v>
@@ -6442,13 +6034,13 @@
         <v>19600</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F104" s="6">
         <v>48600</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H104" s="6">
         <v>36</v>
@@ -6465,13 +6057,13 @@
         <v>20800</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F105" s="7">
         <v>60000</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H105" s="7">
         <v>40</v>
@@ -6488,13 +6080,13 @@
         <v>10000</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F106" s="6">
         <v>600</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H106" s="6">
         <v>4</v>
@@ -6511,13 +6103,13 @@
         <v>11200</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F107" s="7">
         <v>2400</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H107" s="7">
         <v>8</v>
@@ -6534,13 +6126,13 @@
         <v>12400</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F108" s="6">
         <v>5400</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H108" s="6">
         <v>12</v>
@@ -6557,13 +6149,13 @@
         <v>13600</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F109" s="7">
         <v>9600</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H109" s="7">
         <v>16</v>
@@ -6580,13 +6172,13 @@
         <v>14800</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F110" s="6">
         <v>15000</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H110" s="6">
         <v>20</v>
@@ -6603,13 +6195,13 @@
         <v>16000</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F111" s="7">
         <v>21600</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H111" s="7">
         <v>24</v>
@@ -6626,13 +6218,13 @@
         <v>17200</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F112" s="6">
         <v>29400</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H112" s="6">
         <v>28</v>
@@ -6649,13 +6241,13 @@
         <v>18400</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F113" s="7">
         <v>38400</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H113" s="7">
         <v>32</v>
@@ -6672,13 +6264,13 @@
         <v>19600</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F114" s="6">
         <v>48600</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H114" s="6">
         <v>36</v>
@@ -6695,13 +6287,13 @@
         <v>20800</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F115" s="7">
         <v>60000</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H115" s="7">
         <v>40</v>
@@ -6718,13 +6310,13 @@
         <v>10000</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F116" s="6">
         <v>600</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H116" s="6">
         <v>4</v>
@@ -6741,13 +6333,13 @@
         <v>11200</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F117" s="7">
         <v>2400</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H117" s="7">
         <v>8</v>
@@ -6764,13 +6356,13 @@
         <v>12400</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F118" s="6">
         <v>5400</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H118" s="6">
         <v>12</v>
@@ -6787,13 +6379,13 @@
         <v>13600</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F119" s="7">
         <v>9600</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H119" s="7">
         <v>16</v>
@@ -6810,13 +6402,13 @@
         <v>14800</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F120" s="6">
         <v>15000</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H120" s="6">
         <v>20</v>
@@ -6833,13 +6425,13 @@
         <v>16000</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F121" s="7">
         <v>21600</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H121" s="7">
         <v>24</v>
@@ -6856,13 +6448,13 @@
         <v>17200</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F122" s="6">
         <v>29400</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H122" s="6">
         <v>28</v>
@@ -6879,13 +6471,13 @@
         <v>18400</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F123" s="7">
         <v>38400</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H123" s="7">
         <v>32</v>
@@ -6902,13 +6494,13 @@
         <v>19600</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F124" s="6">
         <v>48600</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H124" s="6">
         <v>36</v>
@@ -6925,13 +6517,13 @@
         <v>20800</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F125" s="7">
         <v>60000</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H125" s="7">
         <v>40</v>
@@ -6948,13 +6540,13 @@
         <v>10000</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F126" s="6">
         <v>600</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H126" s="6">
         <v>4</v>
@@ -6971,13 +6563,13 @@
         <v>11200</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F127" s="7">
         <v>2400</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H127" s="7">
         <v>8</v>
@@ -6994,13 +6586,13 @@
         <v>12400</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F128" s="6">
         <v>5400</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H128" s="6">
         <v>12</v>
@@ -7017,13 +6609,13 @@
         <v>13600</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F129" s="7">
         <v>9600</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H129" s="7">
         <v>16</v>
@@ -7040,13 +6632,13 @@
         <v>14800</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F130" s="6">
         <v>15000</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H130" s="6">
         <v>20</v>
@@ -7063,13 +6655,13 @@
         <v>16000</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F131" s="7">
         <v>21600</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H131" s="7">
         <v>24</v>
@@ -7086,13 +6678,13 @@
         <v>17200</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F132" s="6">
         <v>29400</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H132" s="6">
         <v>28</v>
@@ -7109,13 +6701,13 @@
         <v>18400</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F133" s="7">
         <v>38400</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H133" s="7">
         <v>32</v>
@@ -7132,13 +6724,13 @@
         <v>19600</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F134" s="6">
         <v>48600</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H134" s="6">
         <v>36</v>
@@ -7155,13 +6747,13 @@
         <v>20800</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F135" s="7">
         <v>60000</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H135" s="7">
         <v>40</v>
@@ -7178,13 +6770,13 @@
         <v>10000</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F136" s="6">
         <v>600</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H136" s="6">
         <v>4</v>
@@ -7201,13 +6793,13 @@
         <v>11200</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F137" s="7">
         <v>2400</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H137" s="7">
         <v>8</v>
@@ -7224,13 +6816,13 @@
         <v>12400</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F138" s="6">
         <v>5400</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H138" s="6">
         <v>12</v>
@@ -7247,13 +6839,13 @@
         <v>13600</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F139" s="7">
         <v>9600</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H139" s="7">
         <v>16</v>
@@ -7270,13 +6862,13 @@
         <v>14800</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F140" s="6">
         <v>15000</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H140" s="6">
         <v>20</v>
@@ -7293,13 +6885,13 @@
         <v>16000</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F141" s="7">
         <v>21600</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H141" s="7">
         <v>24</v>
@@ -7316,13 +6908,13 @@
         <v>17200</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F142" s="6">
         <v>29400</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H142" s="6">
         <v>28</v>
@@ -7339,13 +6931,13 @@
         <v>18400</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F143" s="7">
         <v>38400</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H143" s="7">
         <v>32</v>
@@ -7362,13 +6954,13 @@
         <v>19600</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F144" s="6">
         <v>48600</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H144" s="6">
         <v>36</v>
@@ -7385,13 +6977,13 @@
         <v>20800</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F145" s="7">
         <v>60000</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H145" s="7">
         <v>40</v>
@@ -7408,13 +7000,13 @@
         <v>10000</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F146" s="6">
         <v>600</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H146" s="6">
         <v>4</v>
@@ -7431,13 +7023,13 @@
         <v>11200</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F147" s="7">
         <v>2400</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H147" s="7">
         <v>8</v>
@@ -7454,13 +7046,13 @@
         <v>12400</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F148" s="6">
         <v>5400</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H148" s="6">
         <v>12</v>
@@ -7477,13 +7069,13 @@
         <v>13600</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F149" s="7">
         <v>9600</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H149" s="7">
         <v>16</v>
@@ -7500,13 +7092,13 @@
         <v>14800</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F150" s="6">
         <v>15000</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H150" s="6">
         <v>20</v>
@@ -7523,13 +7115,13 @@
         <v>16000</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F151" s="7">
         <v>21600</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H151" s="7">
         <v>24</v>
@@ -7546,13 +7138,13 @@
         <v>17200</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F152" s="6">
         <v>29400</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H152" s="6">
         <v>28</v>
@@ -7569,13 +7161,13 @@
         <v>18400</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F153" s="7">
         <v>38400</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H153" s="7">
         <v>32</v>
@@ -7592,13 +7184,13 @@
         <v>19600</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F154" s="6">
         <v>48600</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H154" s="6">
         <v>36</v>
@@ -7615,13 +7207,13 @@
         <v>20800</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F155" s="7">
         <v>60000</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H155" s="7">
         <v>40</v>
@@ -7638,13 +7230,13 @@
         <v>10000</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F156" s="6">
         <v>600</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H156" s="6">
         <v>4</v>
@@ -7661,13 +7253,13 @@
         <v>11200</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F157" s="7">
         <v>2400</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H157" s="7">
         <v>8</v>
@@ -7684,13 +7276,13 @@
         <v>12400</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F158" s="6">
         <v>5400</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H158" s="6">
         <v>12</v>
@@ -7707,13 +7299,13 @@
         <v>13600</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F159" s="7">
         <v>9600</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H159" s="7">
         <v>16</v>
@@ -7730,13 +7322,13 @@
         <v>14800</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F160" s="6">
         <v>15000</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H160" s="6">
         <v>20</v>
@@ -7753,13 +7345,13 @@
         <v>16000</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F161" s="7">
         <v>21600</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H161" s="7">
         <v>24</v>
@@ -7776,13 +7368,13 @@
         <v>17200</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F162" s="6">
         <v>29400</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H162" s="6">
         <v>28</v>
@@ -7799,13 +7391,13 @@
         <v>18400</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F163" s="7">
         <v>38400</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H163" s="7">
         <v>32</v>
@@ -7822,13 +7414,13 @@
         <v>19600</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F164" s="6">
         <v>48600</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H164" s="6">
         <v>36</v>
@@ -7845,13 +7437,13 @@
         <v>20800</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F165" s="7">
         <v>60000</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H165" s="7">
         <v>40</v>
@@ -7868,13 +7460,13 @@
         <v>10000</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F166" s="6">
         <v>600</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H166" s="6">
         <v>4</v>
@@ -7891,13 +7483,13 @@
         <v>11200</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F167" s="7">
         <v>2400</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H167" s="7">
         <v>8</v>
@@ -7914,13 +7506,13 @@
         <v>12400</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F168" s="6">
         <v>5400</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H168" s="6">
         <v>12</v>
@@ -7937,13 +7529,13 @@
         <v>13600</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F169" s="7">
         <v>9600</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H169" s="7">
         <v>16</v>
@@ -7960,13 +7552,13 @@
         <v>14800</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F170" s="6">
         <v>15000</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H170" s="6">
         <v>20</v>
@@ -7983,13 +7575,13 @@
         <v>16000</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F171" s="7">
         <v>21600</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H171" s="7">
         <v>24</v>
@@ -8006,13 +7598,13 @@
         <v>17200</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F172" s="6">
         <v>29400</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H172" s="6">
         <v>28</v>
@@ -8029,13 +7621,13 @@
         <v>18400</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F173" s="7">
         <v>38400</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H173" s="7">
         <v>32</v>
@@ -8052,13 +7644,13 @@
         <v>19600</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F174" s="6">
         <v>48600</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H174" s="6">
         <v>36</v>
@@ -8075,13 +7667,13 @@
         <v>20800</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F175" s="7">
         <v>60000</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H175" s="7">
         <v>40</v>
@@ -8098,13 +7690,13 @@
         <v>10000</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F176" s="6">
         <v>600</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H176" s="6">
         <v>4</v>
@@ -8121,13 +7713,13 @@
         <v>11200</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F177" s="7">
         <v>2400</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H177" s="7">
         <v>8</v>
@@ -8144,13 +7736,13 @@
         <v>12400</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F178" s="6">
         <v>5400</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H178" s="6">
         <v>12</v>
@@ -8167,13 +7759,13 @@
         <v>13600</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F179" s="7">
         <v>9600</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H179" s="7">
         <v>16</v>
@@ -8190,13 +7782,13 @@
         <v>14800</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F180" s="6">
         <v>15000</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H180" s="6">
         <v>20</v>
@@ -8213,13 +7805,13 @@
         <v>16000</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F181" s="7">
         <v>21600</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H181" s="7">
         <v>24</v>
@@ -8236,13 +7828,13 @@
         <v>17200</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F182" s="6">
         <v>29400</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H182" s="6">
         <v>28</v>
@@ -8259,13 +7851,13 @@
         <v>18400</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F183" s="7">
         <v>38400</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H183" s="7">
         <v>32</v>
@@ -8282,13 +7874,13 @@
         <v>19600</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F184" s="6">
         <v>48600</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H184" s="6">
         <v>36</v>
@@ -8305,13 +7897,13 @@
         <v>20800</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F185" s="7">
         <v>60000</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H185" s="7">
         <v>40</v>
@@ -8328,13 +7920,13 @@
         <v>10000</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F186" s="6">
         <v>600</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H186" s="6">
         <v>4</v>
@@ -8351,13 +7943,13 @@
         <v>11200</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F187" s="7">
         <v>2400</v>
       </c>
       <c r="G187" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H187" s="7">
         <v>8</v>
@@ -8374,13 +7966,13 @@
         <v>12400</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F188" s="6">
         <v>5400</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H188" s="6">
         <v>12</v>
@@ -8397,13 +7989,13 @@
         <v>13600</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F189" s="7">
         <v>9600</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H189" s="7">
         <v>16</v>
@@ -8420,13 +8012,13 @@
         <v>14800</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F190" s="6">
         <v>15000</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H190" s="6">
         <v>20</v>
@@ -8443,13 +8035,13 @@
         <v>16000</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F191" s="7">
         <v>21600</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H191" s="7">
         <v>24</v>
@@ -8466,13 +8058,13 @@
         <v>17200</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F192" s="6">
         <v>29400</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H192" s="6">
         <v>28</v>
@@ -8489,13 +8081,13 @@
         <v>18400</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F193" s="7">
         <v>38400</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H193" s="7">
         <v>32</v>
@@ -8512,13 +8104,13 @@
         <v>19600</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F194" s="6">
         <v>48600</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H194" s="6">
         <v>36</v>
@@ -8535,13 +8127,13 @@
         <v>20800</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F195" s="7">
         <v>60000</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H195" s="7">
         <v>40</v>
@@ -8558,13 +8150,13 @@
         <v>10000</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F196" s="6">
         <v>600</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H196" s="6">
         <v>4</v>
@@ -8581,13 +8173,13 @@
         <v>11200</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F197" s="7">
         <v>2400</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H197" s="7">
         <v>8</v>
@@ -8604,13 +8196,13 @@
         <v>12400</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F198" s="6">
         <v>5400</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H198" s="6">
         <v>12</v>
@@ -8627,13 +8219,13 @@
         <v>13600</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F199" s="7">
         <v>9600</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H199" s="7">
         <v>16</v>
@@ -8650,13 +8242,13 @@
         <v>14800</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F200" s="6">
         <v>15000</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H200" s="6">
         <v>20</v>
@@ -8673,13 +8265,13 @@
         <v>16000</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F201" s="7">
         <v>21600</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H201" s="7">
         <v>24</v>
@@ -8696,13 +8288,13 @@
         <v>17200</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F202" s="6">
         <v>29400</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H202" s="6">
         <v>28</v>
@@ -8719,13 +8311,13 @@
         <v>18400</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F203" s="7">
         <v>38400</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H203" s="7">
         <v>32</v>
@@ -8742,13 +8334,13 @@
         <v>19600</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F204" s="6">
         <v>48600</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H204" s="6">
         <v>36</v>
@@ -8765,13 +8357,13 @@
         <v>20800</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F205" s="7">
         <v>60000</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H205" s="7">
         <v>40</v>
@@ -8788,13 +8380,13 @@
         <v>10000</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F206" s="6">
         <v>600</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H206" s="6">
         <v>4</v>
@@ -8811,13 +8403,13 @@
         <v>11200</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F207" s="7">
         <v>2400</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H207" s="7">
         <v>8</v>
@@ -8834,13 +8426,13 @@
         <v>12400</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F208" s="6">
         <v>5400</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H208" s="6">
         <v>12</v>
@@ -8857,13 +8449,13 @@
         <v>13600</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F209" s="7">
         <v>9600</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H209" s="7">
         <v>16</v>
@@ -8880,13 +8472,13 @@
         <v>14800</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F210" s="6">
         <v>15000</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H210" s="6">
         <v>20</v>
@@ -8903,13 +8495,13 @@
         <v>16000</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F211" s="7">
         <v>21600</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H211" s="7">
         <v>24</v>
@@ -8926,13 +8518,13 @@
         <v>17200</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F212" s="6">
         <v>29400</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H212" s="6">
         <v>28</v>
@@ -8949,13 +8541,13 @@
         <v>18400</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F213" s="7">
         <v>38400</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H213" s="7">
         <v>32</v>
@@ -8972,13 +8564,13 @@
         <v>19600</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F214" s="6">
         <v>48600</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H214" s="6">
         <v>36</v>
@@ -8995,13 +8587,13 @@
         <v>20800</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F215" s="7">
         <v>60000</v>
       </c>
       <c r="G215" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H215" s="7">
         <v>40</v>
@@ -9018,13 +8610,13 @@
         <v>10000</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F216" s="6">
         <v>600</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H216" s="6">
         <v>4</v>
@@ -9041,13 +8633,13 @@
         <v>11200</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F217" s="7">
         <v>2400</v>
       </c>
       <c r="G217" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H217" s="7">
         <v>8</v>
@@ -9064,13 +8656,13 @@
         <v>12400</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F218" s="6">
         <v>5400</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H218" s="6">
         <v>12</v>
@@ -9087,13 +8679,13 @@
         <v>13600</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F219" s="7">
         <v>9600</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H219" s="7">
         <v>16</v>
@@ -9110,13 +8702,13 @@
         <v>14800</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F220" s="6">
         <v>15000</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H220" s="6">
         <v>20</v>
@@ -9133,13 +8725,13 @@
         <v>16000</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F221" s="7">
         <v>21600</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H221" s="7">
         <v>24</v>
@@ -9156,13 +8748,13 @@
         <v>17200</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F222" s="6">
         <v>29400</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H222" s="6">
         <v>28</v>
@@ -9179,13 +8771,13 @@
         <v>18400</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F223" s="7">
         <v>38400</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H223" s="7">
         <v>32</v>
@@ -9202,13 +8794,13 @@
         <v>19600</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F224" s="6">
         <v>48600</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H224" s="6">
         <v>36</v>
@@ -9225,13 +8817,13 @@
         <v>20800</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F225" s="7">
         <v>60000</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H225" s="7">
         <v>40</v>
@@ -9248,13 +8840,13 @@
         <v>10000</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F226" s="6">
         <v>600</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H226" s="6">
         <v>4</v>
@@ -9271,13 +8863,13 @@
         <v>11200</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F227" s="7">
         <v>2400</v>
       </c>
       <c r="G227" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H227" s="7">
         <v>8</v>
@@ -9294,13 +8886,13 @@
         <v>12400</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F228" s="6">
         <v>5400</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H228" s="6">
         <v>12</v>
@@ -9317,13 +8909,13 @@
         <v>13600</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F229" s="7">
         <v>9600</v>
       </c>
       <c r="G229" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H229" s="7">
         <v>16</v>
@@ -9340,13 +8932,13 @@
         <v>14800</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F230" s="6">
         <v>15000</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H230" s="6">
         <v>20</v>
@@ -9363,13 +8955,13 @@
         <v>16000</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F231" s="7">
         <v>21600</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H231" s="7">
         <v>24</v>
@@ -9386,13 +8978,13 @@
         <v>17200</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F232" s="6">
         <v>29400</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H232" s="6">
         <v>28</v>
@@ -9409,13 +9001,13 @@
         <v>18400</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F233" s="7">
         <v>38400</v>
       </c>
       <c r="G233" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H233" s="7">
         <v>32</v>
@@ -9432,13 +9024,13 @@
         <v>19600</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F234" s="6">
         <v>48600</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H234" s="6">
         <v>36</v>
@@ -9455,13 +9047,13 @@
         <v>20800</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F235" s="7">
         <v>60000</v>
       </c>
       <c r="G235" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H235" s="7">
         <v>40</v>
@@ -9478,13 +9070,13 @@
         <v>10000</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F236" s="6">
         <v>600</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H236" s="6">
         <v>4</v>
@@ -9501,13 +9093,13 @@
         <v>11200</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F237" s="7">
         <v>2400</v>
       </c>
       <c r="G237" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H237" s="7">
         <v>8</v>
@@ -9524,13 +9116,13 @@
         <v>12400</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F238" s="6">
         <v>5400</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H238" s="6">
         <v>12</v>
@@ -9547,13 +9139,13 @@
         <v>13600</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F239" s="7">
         <v>9600</v>
       </c>
       <c r="G239" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H239" s="7">
         <v>16</v>
@@ -9570,13 +9162,13 @@
         <v>14800</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F240" s="6">
         <v>15000</v>
       </c>
       <c r="G240" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H240" s="6">
         <v>20</v>
@@ -9593,13 +9185,13 @@
         <v>16000</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F241" s="7">
         <v>21600</v>
       </c>
       <c r="G241" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H241" s="7">
         <v>24</v>
@@ -9616,13 +9208,13 @@
         <v>17200</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F242" s="6">
         <v>29400</v>
       </c>
       <c r="G242" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H242" s="6">
         <v>28</v>
@@ -9639,13 +9231,13 @@
         <v>18400</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F243" s="7">
         <v>38400</v>
       </c>
       <c r="G243" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H243" s="7">
         <v>32</v>
@@ -9662,13 +9254,13 @@
         <v>19600</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F244" s="6">
         <v>48600</v>
       </c>
       <c r="G244" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H244" s="6">
         <v>36</v>
@@ -9685,13 +9277,13 @@
         <v>20800</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F245" s="7">
         <v>60000</v>
       </c>
       <c r="G245" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H245" s="7">
         <v>40</v>
@@ -9708,13 +9300,13 @@
         <v>10000</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F246" s="6">
         <v>600</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H246" s="6">
         <v>4</v>
@@ -9731,13 +9323,13 @@
         <v>11200</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F247" s="7">
         <v>2400</v>
       </c>
       <c r="G247" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H247" s="7">
         <v>8</v>
@@ -9754,13 +9346,13 @@
         <v>12400</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F248" s="6">
         <v>5400</v>
       </c>
       <c r="G248" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H248" s="6">
         <v>12</v>
@@ -9777,13 +9369,13 @@
         <v>13600</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F249" s="7">
         <v>9600</v>
       </c>
       <c r="G249" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H249" s="7">
         <v>16</v>
@@ -9800,13 +9392,13 @@
         <v>14800</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F250" s="6">
         <v>15000</v>
       </c>
       <c r="G250" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H250" s="6">
         <v>20</v>
@@ -9823,13 +9415,13 @@
         <v>16000</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F251" s="7">
         <v>21600</v>
       </c>
       <c r="G251" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H251" s="7">
         <v>24</v>
@@ -9846,13 +9438,13 @@
         <v>17200</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F252" s="6">
         <v>29400</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H252" s="6">
         <v>28</v>
@@ -9869,13 +9461,13 @@
         <v>18400</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F253" s="7">
         <v>38400</v>
       </c>
       <c r="G253" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H253" s="7">
         <v>32</v>
@@ -9892,13 +9484,13 @@
         <v>19600</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F254" s="6">
         <v>48600</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H254" s="6">
         <v>36</v>
@@ -9915,13 +9507,13 @@
         <v>20800</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F255" s="7">
         <v>60000</v>
       </c>
       <c r="G255" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H255" s="7">
         <v>40</v>
@@ -9938,13 +9530,13 @@
         <v>10000</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F256" s="6">
         <v>600</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H256" s="6">
         <v>4</v>
@@ -9961,13 +9553,13 @@
         <v>11200</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F257" s="7">
         <v>2400</v>
       </c>
       <c r="G257" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H257" s="7">
         <v>8</v>
@@ -9984,13 +9576,13 @@
         <v>12400</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F258" s="6">
         <v>5400</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H258" s="6">
         <v>12</v>
@@ -10007,13 +9599,13 @@
         <v>13600</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F259" s="7">
         <v>9600</v>
       </c>
       <c r="G259" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H259" s="7">
         <v>16</v>
@@ -10030,13 +9622,13 @@
         <v>14800</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F260" s="6">
         <v>15000</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H260" s="6">
         <v>20</v>
@@ -10053,13 +9645,13 @@
         <v>16000</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F261" s="7">
         <v>21600</v>
       </c>
       <c r="G261" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H261" s="7">
         <v>24</v>
@@ -10076,13 +9668,13 @@
         <v>17200</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F262" s="6">
         <v>29400</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H262" s="6">
         <v>28</v>
@@ -10099,13 +9691,13 @@
         <v>18400</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F263" s="7">
         <v>38400</v>
       </c>
       <c r="G263" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H263" s="7">
         <v>32</v>
@@ -10122,13 +9714,13 @@
         <v>19600</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F264" s="6">
         <v>48600</v>
       </c>
       <c r="G264" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H264" s="6">
         <v>36</v>
@@ -10145,13 +9737,13 @@
         <v>20800</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F265" s="7">
         <v>60000</v>
       </c>
       <c r="G265" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H265" s="7">
         <v>40</v>
@@ -10168,13 +9760,13 @@
         <v>10000</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F266" s="6">
         <v>600</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H266" s="6">
         <v>4</v>
@@ -10191,13 +9783,13 @@
         <v>11200</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F267" s="7">
         <v>2400</v>
       </c>
       <c r="G267" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H267" s="7">
         <v>8</v>
@@ -10214,13 +9806,13 @@
         <v>12400</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F268" s="6">
         <v>5400</v>
       </c>
       <c r="G268" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H268" s="6">
         <v>12</v>
@@ -10237,13 +9829,13 @@
         <v>13600</v>
       </c>
       <c r="E269" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F269" s="7">
         <v>9600</v>
       </c>
       <c r="G269" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H269" s="7">
         <v>16</v>
@@ -10260,13 +9852,13 @@
         <v>14800</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F270" s="6">
         <v>15000</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H270" s="6">
         <v>20</v>
@@ -10283,13 +9875,13 @@
         <v>16000</v>
       </c>
       <c r="E271" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F271" s="7">
         <v>21600</v>
       </c>
       <c r="G271" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H271" s="7">
         <v>24</v>
@@ -10306,13 +9898,13 @@
         <v>17200</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F272" s="6">
         <v>29400</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H272" s="6">
         <v>28</v>
@@ -10329,13 +9921,13 @@
         <v>18400</v>
       </c>
       <c r="E273" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F273" s="7">
         <v>38400</v>
       </c>
       <c r="G273" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H273" s="7">
         <v>32</v>
@@ -10352,13 +9944,13 @@
         <v>19600</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F274" s="6">
         <v>48600</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H274" s="6">
         <v>36</v>
@@ -10375,13 +9967,13 @@
         <v>20800</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F275" s="7">
         <v>60000</v>
       </c>
       <c r="G275" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H275" s="7">
         <v>40</v>
@@ -10398,13 +9990,13 @@
         <v>10000</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F276" s="6">
         <v>600</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H276" s="6">
         <v>4</v>
@@ -10421,13 +10013,13 @@
         <v>11200</v>
       </c>
       <c r="E277" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F277" s="7">
         <v>2400</v>
       </c>
       <c r="G277" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H277" s="7">
         <v>8</v>
@@ -10444,13 +10036,13 @@
         <v>12400</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F278" s="6">
         <v>5400</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H278" s="6">
         <v>12</v>
@@ -10467,13 +10059,13 @@
         <v>13600</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F279" s="7">
         <v>9600</v>
       </c>
       <c r="G279" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H279" s="7">
         <v>16</v>
@@ -10490,13 +10082,13 @@
         <v>14800</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F280" s="6">
         <v>15000</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H280" s="6">
         <v>20</v>
@@ -10513,13 +10105,13 @@
         <v>16000</v>
       </c>
       <c r="E281" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F281" s="7">
         <v>21600</v>
       </c>
       <c r="G281" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H281" s="7">
         <v>24</v>
@@ -10536,13 +10128,13 @@
         <v>17200</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F282" s="6">
         <v>29400</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H282" s="6">
         <v>28</v>
@@ -10559,13 +10151,13 @@
         <v>18400</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F283" s="7">
         <v>38400</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H283" s="7">
         <v>32</v>
@@ -10582,13 +10174,13 @@
         <v>19600</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F284" s="6">
         <v>48600</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H284" s="6">
         <v>36</v>
@@ -10605,13 +10197,13 @@
         <v>20800</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F285" s="7">
         <v>60000</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H285" s="7">
         <v>40</v>
@@ -10628,13 +10220,13 @@
         <v>10000</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F286" s="6">
         <v>600</v>
       </c>
       <c r="G286" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H286" s="6">
         <v>4</v>
@@ -10651,13 +10243,13 @@
         <v>11200</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F287" s="7">
         <v>2400</v>
       </c>
       <c r="G287" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H287" s="7">
         <v>8</v>
@@ -10674,13 +10266,13 @@
         <v>12400</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F288" s="6">
         <v>5400</v>
       </c>
       <c r="G288" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H288" s="6">
         <v>12</v>
@@ -10697,13 +10289,13 @@
         <v>13600</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F289" s="7">
         <v>9600</v>
       </c>
       <c r="G289" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H289" s="7">
         <v>16</v>
@@ -10720,13 +10312,13 @@
         <v>14800</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F290" s="6">
         <v>15000</v>
       </c>
       <c r="G290" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H290" s="6">
         <v>20</v>
@@ -10743,13 +10335,13 @@
         <v>16000</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F291" s="7">
         <v>21600</v>
       </c>
       <c r="G291" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H291" s="7">
         <v>24</v>
@@ -10766,13 +10358,13 @@
         <v>17200</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F292" s="6">
         <v>29400</v>
       </c>
       <c r="G292" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H292" s="6">
         <v>28</v>
@@ -10789,13 +10381,13 @@
         <v>18400</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F293" s="7">
         <v>38400</v>
       </c>
       <c r="G293" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H293" s="7">
         <v>32</v>
@@ -10812,13 +10404,13 @@
         <v>19600</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F294" s="6">
         <v>48600</v>
       </c>
       <c r="G294" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H294" s="6">
         <v>36</v>
@@ -10835,13 +10427,13 @@
         <v>20800</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F295" s="7">
         <v>60000</v>
       </c>
       <c r="G295" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H295" s="7">
         <v>40</v>
@@ -10858,13 +10450,13 @@
         <v>10000</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F296" s="6">
         <v>600</v>
       </c>
       <c r="G296" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H296" s="6">
         <v>4</v>
@@ -10881,13 +10473,13 @@
         <v>11200</v>
       </c>
       <c r="E297" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F297" s="7">
         <v>2400</v>
       </c>
       <c r="G297" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H297" s="7">
         <v>8</v>
@@ -10904,13 +10496,13 @@
         <v>12400</v>
       </c>
       <c r="E298" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F298" s="6">
         <v>5400</v>
       </c>
       <c r="G298" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H298" s="6">
         <v>12</v>
@@ -10927,13 +10519,13 @@
         <v>13600</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F299" s="7">
         <v>9600</v>
       </c>
       <c r="G299" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H299" s="7">
         <v>16</v>
@@ -10950,13 +10542,13 @@
         <v>14800</v>
       </c>
       <c r="E300" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F300" s="6">
         <v>15000</v>
       </c>
       <c r="G300" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H300" s="6">
         <v>20</v>
@@ -10973,13 +10565,13 @@
         <v>16000</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F301" s="7">
         <v>21600</v>
       </c>
       <c r="G301" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H301" s="7">
         <v>24</v>
@@ -10996,13 +10588,13 @@
         <v>17200</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F302" s="6">
         <v>29400</v>
       </c>
       <c r="G302" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H302" s="6">
         <v>28</v>
@@ -11019,13 +10611,13 @@
         <v>18400</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F303" s="7">
         <v>38400</v>
       </c>
       <c r="G303" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H303" s="7">
         <v>32</v>
@@ -11042,13 +10634,13 @@
         <v>19600</v>
       </c>
       <c r="E304" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F304" s="6">
         <v>48600</v>
       </c>
       <c r="G304" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H304" s="6">
         <v>36</v>
@@ -11065,13 +10657,13 @@
         <v>20800</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F305" s="7">
         <v>60000</v>
       </c>
       <c r="G305" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H305" s="7">
         <v>40</v>
@@ -11088,13 +10680,13 @@
         <v>10000</v>
       </c>
       <c r="E306" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F306" s="6">
         <v>600</v>
       </c>
       <c r="G306" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H306" s="6">
         <v>4</v>
@@ -11111,13 +10703,13 @@
         <v>11200</v>
       </c>
       <c r="E307" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F307" s="7">
         <v>2400</v>
       </c>
       <c r="G307" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H307" s="7">
         <v>8</v>
@@ -11134,13 +10726,13 @@
         <v>12400</v>
       </c>
       <c r="E308" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F308" s="6">
         <v>5400</v>
       </c>
       <c r="G308" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H308" s="6">
         <v>12</v>
@@ -11157,13 +10749,13 @@
         <v>13600</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F309" s="7">
         <v>9600</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H309" s="7">
         <v>16</v>
@@ -11180,13 +10772,13 @@
         <v>14800</v>
       </c>
       <c r="E310" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F310" s="6">
         <v>15000</v>
       </c>
       <c r="G310" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H310" s="6">
         <v>20</v>
@@ -11203,13 +10795,13 @@
         <v>16000</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F311" s="7">
         <v>21600</v>
       </c>
       <c r="G311" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H311" s="7">
         <v>24</v>
@@ -11226,13 +10818,13 @@
         <v>17200</v>
       </c>
       <c r="E312" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F312" s="6">
         <v>29400</v>
       </c>
       <c r="G312" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H312" s="6">
         <v>28</v>
@@ -11249,13 +10841,13 @@
         <v>18400</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F313" s="7">
         <v>38400</v>
       </c>
       <c r="G313" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H313" s="7">
         <v>32</v>
@@ -11272,13 +10864,13 @@
         <v>19600</v>
       </c>
       <c r="E314" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F314" s="6">
         <v>48600</v>
       </c>
       <c r="G314" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H314" s="6">
         <v>36</v>
@@ -11295,13 +10887,13 @@
         <v>20800</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F315" s="7">
         <v>60000</v>
       </c>
       <c r="G315" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H315" s="7">
         <v>40</v>
@@ -11318,13 +10910,13 @@
         <v>10000</v>
       </c>
       <c r="E316" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F316" s="6">
         <v>600</v>
       </c>
       <c r="G316" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H316" s="6">
         <v>4</v>
@@ -11341,13 +10933,13 @@
         <v>11200</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F317" s="7">
         <v>2400</v>
       </c>
       <c r="G317" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H317" s="7">
         <v>8</v>
@@ -11364,13 +10956,13 @@
         <v>12400</v>
       </c>
       <c r="E318" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F318" s="6">
         <v>5400</v>
       </c>
       <c r="G318" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H318" s="6">
         <v>12</v>
@@ -11387,13 +10979,13 @@
         <v>13600</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F319" s="7">
         <v>9600</v>
       </c>
       <c r="G319" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H319" s="7">
         <v>16</v>
@@ -11410,13 +11002,13 @@
         <v>14800</v>
       </c>
       <c r="E320" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F320" s="6">
         <v>15000</v>
       </c>
       <c r="G320" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H320" s="6">
         <v>20</v>
@@ -11433,13 +11025,13 @@
         <v>16000</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F321" s="7">
         <v>21600</v>
       </c>
       <c r="G321" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H321" s="7">
         <v>24</v>
@@ -11456,13 +11048,13 @@
         <v>17200</v>
       </c>
       <c r="E322" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F322" s="6">
         <v>29400</v>
       </c>
       <c r="G322" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H322" s="6">
         <v>28</v>
@@ -11479,13 +11071,13 @@
         <v>18400</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F323" s="7">
         <v>38400</v>
       </c>
       <c r="G323" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H323" s="7">
         <v>32</v>
@@ -11502,13 +11094,13 @@
         <v>19600</v>
       </c>
       <c r="E324" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F324" s="6">
         <v>48600</v>
       </c>
       <c r="G324" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H324" s="6">
         <v>36</v>
@@ -11525,13 +11117,13 @@
         <v>20800</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F325" s="7">
         <v>60000</v>
       </c>
       <c r="G325" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H325" s="7">
         <v>40</v>
@@ -11548,13 +11140,13 @@
         <v>10000</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F326" s="6">
         <v>600</v>
       </c>
       <c r="G326" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H326" s="6">
         <v>4</v>
@@ -11571,13 +11163,13 @@
         <v>11200</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F327" s="7">
         <v>2400</v>
       </c>
       <c r="G327" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H327" s="7">
         <v>8</v>
@@ -11594,13 +11186,13 @@
         <v>12400</v>
       </c>
       <c r="E328" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F328" s="6">
         <v>5400</v>
       </c>
       <c r="G328" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H328" s="6">
         <v>12</v>
@@ -11617,13 +11209,13 @@
         <v>13600</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F329" s="7">
         <v>9600</v>
       </c>
       <c r="G329" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H329" s="7">
         <v>16</v>
@@ -11640,13 +11232,13 @@
         <v>14800</v>
       </c>
       <c r="E330" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F330" s="6">
         <v>15000</v>
       </c>
       <c r="G330" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H330" s="6">
         <v>20</v>
@@ -11663,13 +11255,13 @@
         <v>16000</v>
       </c>
       <c r="E331" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F331" s="7">
         <v>21600</v>
       </c>
       <c r="G331" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H331" s="7">
         <v>24</v>
@@ -11686,13 +11278,13 @@
         <v>17200</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F332" s="6">
         <v>29400</v>
       </c>
       <c r="G332" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H332" s="6">
         <v>28</v>
@@ -11709,13 +11301,13 @@
         <v>18400</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F333" s="7">
         <v>38400</v>
       </c>
       <c r="G333" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H333" s="7">
         <v>32</v>
@@ -11732,13 +11324,13 @@
         <v>19600</v>
       </c>
       <c r="E334" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F334" s="6">
         <v>48600</v>
       </c>
       <c r="G334" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H334" s="6">
         <v>36</v>
@@ -11755,13 +11347,13 @@
         <v>20800</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F335" s="7">
         <v>60000</v>
       </c>
       <c r="G335" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H335" s="7">
         <v>40</v>
@@ -11778,13 +11370,13 @@
         <v>10000</v>
       </c>
       <c r="E336" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F336" s="6">
         <v>600</v>
       </c>
       <c r="G336" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H336" s="6">
         <v>4</v>
@@ -11801,13 +11393,13 @@
         <v>11200</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F337" s="7">
         <v>2400</v>
       </c>
       <c r="G337" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H337" s="7">
         <v>8</v>
@@ -11824,13 +11416,13 @@
         <v>12400</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F338" s="6">
         <v>5400</v>
       </c>
       <c r="G338" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H338" s="6">
         <v>12</v>
@@ -11847,13 +11439,13 @@
         <v>13600</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F339" s="7">
         <v>9600</v>
       </c>
       <c r="G339" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H339" s="7">
         <v>16</v>
@@ -11870,13 +11462,13 @@
         <v>14800</v>
       </c>
       <c r="E340" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F340" s="6">
         <v>15000</v>
       </c>
       <c r="G340" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H340" s="6">
         <v>20</v>
@@ -11893,13 +11485,13 @@
         <v>16000</v>
       </c>
       <c r="E341" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F341" s="7">
         <v>21600</v>
       </c>
       <c r="G341" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H341" s="7">
         <v>24</v>
@@ -11916,13 +11508,13 @@
         <v>17200</v>
       </c>
       <c r="E342" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F342" s="6">
         <v>29400</v>
       </c>
       <c r="G342" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H342" s="6">
         <v>28</v>
@@ -11939,13 +11531,13 @@
         <v>18400</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F343" s="7">
         <v>38400</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H343" s="7">
         <v>32</v>
@@ -11962,13 +11554,13 @@
         <v>19600</v>
       </c>
       <c r="E344" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F344" s="6">
         <v>48600</v>
       </c>
       <c r="G344" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H344" s="6">
         <v>36</v>
@@ -11985,13 +11577,13 @@
         <v>20800</v>
       </c>
       <c r="E345" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F345" s="7">
         <v>60000</v>
       </c>
       <c r="G345" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H345" s="7">
         <v>40</v>
@@ -12008,13 +11600,13 @@
         <v>10000</v>
       </c>
       <c r="E346" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F346" s="6">
         <v>600</v>
       </c>
       <c r="G346" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H346" s="6">
         <v>4</v>
@@ -12031,13 +11623,13 @@
         <v>11200</v>
       </c>
       <c r="E347" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F347" s="7">
         <v>2400</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H347" s="7">
         <v>8</v>
@@ -12054,13 +11646,13 @@
         <v>12400</v>
       </c>
       <c r="E348" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F348" s="6">
         <v>5400</v>
       </c>
       <c r="G348" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H348" s="6">
         <v>12</v>
@@ -12077,13 +11669,13 @@
         <v>13600</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F349" s="7">
         <v>9600</v>
       </c>
       <c r="G349" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H349" s="7">
         <v>16</v>
@@ -12100,13 +11692,13 @@
         <v>14800</v>
       </c>
       <c r="E350" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F350" s="6">
         <v>15000</v>
       </c>
       <c r="G350" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H350" s="6">
         <v>20</v>
@@ -12123,13 +11715,13 @@
         <v>16000</v>
       </c>
       <c r="E351" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F351" s="7">
         <v>21600</v>
       </c>
       <c r="G351" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H351" s="7">
         <v>24</v>
@@ -12146,13 +11738,13 @@
         <v>17200</v>
       </c>
       <c r="E352" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F352" s="6">
         <v>29400</v>
       </c>
       <c r="G352" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H352" s="6">
         <v>28</v>
@@ -12169,13 +11761,13 @@
         <v>18400</v>
       </c>
       <c r="E353" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F353" s="7">
         <v>38400</v>
       </c>
       <c r="G353" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H353" s="7">
         <v>32</v>
@@ -12192,13 +11784,13 @@
         <v>19600</v>
       </c>
       <c r="E354" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F354" s="6">
         <v>48600</v>
       </c>
       <c r="G354" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H354" s="6">
         <v>36</v>
@@ -12215,13 +11807,13 @@
         <v>20800</v>
       </c>
       <c r="E355" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F355" s="7">
         <v>60000</v>
       </c>
       <c r="G355" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H355" s="7">
         <v>40</v>
@@ -12238,13 +11830,13 @@
         <v>10000</v>
       </c>
       <c r="E356" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F356" s="6">
         <v>600</v>
       </c>
       <c r="G356" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H356" s="6">
         <v>4</v>
@@ -12261,13 +11853,13 @@
         <v>11200</v>
       </c>
       <c r="E357" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F357" s="7">
         <v>2400</v>
       </c>
       <c r="G357" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H357" s="7">
         <v>8</v>
@@ -12284,13 +11876,13 @@
         <v>12400</v>
       </c>
       <c r="E358" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F358" s="6">
         <v>5400</v>
       </c>
       <c r="G358" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H358" s="6">
         <v>12</v>
@@ -12307,13 +11899,13 @@
         <v>13600</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F359" s="7">
         <v>9600</v>
       </c>
       <c r="G359" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H359" s="7">
         <v>16</v>
@@ -12330,13 +11922,13 @@
         <v>14800</v>
       </c>
       <c r="E360" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F360" s="6">
         <v>15000</v>
       </c>
       <c r="G360" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H360" s="6">
         <v>20</v>
@@ -12353,13 +11945,13 @@
         <v>16000</v>
       </c>
       <c r="E361" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F361" s="7">
         <v>21600</v>
       </c>
       <c r="G361" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H361" s="7">
         <v>24</v>
@@ -12376,13 +11968,13 @@
         <v>17200</v>
       </c>
       <c r="E362" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F362" s="6">
         <v>29400</v>
       </c>
       <c r="G362" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H362" s="6">
         <v>28</v>
@@ -12399,13 +11991,13 @@
         <v>18400</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F363" s="7">
         <v>38400</v>
       </c>
       <c r="G363" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H363" s="7">
         <v>32</v>
@@ -12422,13 +12014,13 @@
         <v>19600</v>
       </c>
       <c r="E364" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F364" s="6">
         <v>48600</v>
       </c>
       <c r="G364" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H364" s="6">
         <v>36</v>
@@ -12445,13 +12037,13 @@
         <v>20800</v>
       </c>
       <c r="E365" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F365" s="7">
         <v>60000</v>
       </c>
       <c r="G365" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H365" s="7">
         <v>40</v>
@@ -12468,13 +12060,13 @@
         <v>10000</v>
       </c>
       <c r="E366" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F366" s="6">
         <v>600</v>
       </c>
       <c r="G366" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H366" s="6">
         <v>4</v>
@@ -12491,13 +12083,13 @@
         <v>11200</v>
       </c>
       <c r="E367" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F367" s="7">
         <v>2400</v>
       </c>
       <c r="G367" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H367" s="7">
         <v>8</v>
@@ -12514,13 +12106,13 @@
         <v>12400</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F368" s="6">
         <v>5400</v>
       </c>
       <c r="G368" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H368" s="6">
         <v>12</v>
@@ -12537,13 +12129,13 @@
         <v>13600</v>
       </c>
       <c r="E369" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F369" s="7">
         <v>9600</v>
       </c>
       <c r="G369" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H369" s="7">
         <v>16</v>
@@ -12560,13 +12152,13 @@
         <v>14800</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F370" s="6">
         <v>15000</v>
       </c>
       <c r="G370" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H370" s="6">
         <v>20</v>
@@ -12583,13 +12175,13 @@
         <v>16000</v>
       </c>
       <c r="E371" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F371" s="7">
         <v>21600</v>
       </c>
       <c r="G371" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H371" s="7">
         <v>24</v>
@@ -12606,13 +12198,13 @@
         <v>17200</v>
       </c>
       <c r="E372" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F372" s="6">
         <v>29400</v>
       </c>
       <c r="G372" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H372" s="6">
         <v>28</v>
@@ -12629,13 +12221,13 @@
         <v>18400</v>
       </c>
       <c r="E373" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F373" s="7">
         <v>38400</v>
       </c>
       <c r="G373" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H373" s="7">
         <v>32</v>
@@ -12652,13 +12244,13 @@
         <v>19600</v>
       </c>
       <c r="E374" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F374" s="6">
         <v>48600</v>
       </c>
       <c r="G374" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H374" s="6">
         <v>36</v>
@@ -12675,13 +12267,13 @@
         <v>20800</v>
       </c>
       <c r="E375" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F375" s="7">
         <v>60000</v>
       </c>
       <c r="G375" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H375" s="7">
         <v>40</v>
@@ -12698,13 +12290,13 @@
         <v>10000</v>
       </c>
       <c r="E376" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F376" s="6">
         <v>600</v>
       </c>
       <c r="G376" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H376" s="6">
         <v>4</v>
@@ -12721,13 +12313,13 @@
         <v>11200</v>
       </c>
       <c r="E377" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F377" s="7">
         <v>2400</v>
       </c>
       <c r="G377" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H377" s="7">
         <v>8</v>
@@ -12744,13 +12336,13 @@
         <v>12400</v>
       </c>
       <c r="E378" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F378" s="6">
         <v>5400</v>
       </c>
       <c r="G378" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H378" s="6">
         <v>12</v>
@@ -12767,13 +12359,13 @@
         <v>13600</v>
       </c>
       <c r="E379" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F379" s="7">
         <v>9600</v>
       </c>
       <c r="G379" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H379" s="7">
         <v>16</v>
@@ -12790,13 +12382,13 @@
         <v>14800</v>
       </c>
       <c r="E380" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F380" s="6">
         <v>15000</v>
       </c>
       <c r="G380" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H380" s="6">
         <v>20</v>
@@ -12813,13 +12405,13 @@
         <v>16000</v>
       </c>
       <c r="E381" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F381" s="7">
         <v>21600</v>
       </c>
       <c r="G381" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H381" s="7">
         <v>24</v>
@@ -12836,13 +12428,13 @@
         <v>17200</v>
       </c>
       <c r="E382" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F382" s="6">
         <v>29400</v>
       </c>
       <c r="G382" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H382" s="6">
         <v>28</v>
@@ -12859,13 +12451,13 @@
         <v>18400</v>
       </c>
       <c r="E383" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F383" s="7">
         <v>38400</v>
       </c>
       <c r="G383" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H383" s="7">
         <v>32</v>
@@ -12882,13 +12474,13 @@
         <v>19600</v>
       </c>
       <c r="E384" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F384" s="6">
         <v>48600</v>
       </c>
       <c r="G384" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H384" s="6">
         <v>36</v>
@@ -12905,13 +12497,13 @@
         <v>20800</v>
       </c>
       <c r="E385" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F385" s="7">
         <v>60000</v>
       </c>
       <c r="G385" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H385" s="7">
         <v>40</v>
@@ -12928,13 +12520,13 @@
         <v>10000</v>
       </c>
       <c r="E386" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F386" s="6">
         <v>600</v>
       </c>
       <c r="G386" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H386" s="6">
         <v>4</v>
@@ -12951,13 +12543,13 @@
         <v>11200</v>
       </c>
       <c r="E387" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F387" s="7">
         <v>2400</v>
       </c>
       <c r="G387" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H387" s="7">
         <v>8</v>
@@ -12974,13 +12566,13 @@
         <v>12400</v>
       </c>
       <c r="E388" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F388" s="6">
         <v>5400</v>
       </c>
       <c r="G388" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H388" s="6">
         <v>12</v>
@@ -12997,13 +12589,13 @@
         <v>13600</v>
       </c>
       <c r="E389" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F389" s="7">
         <v>9600</v>
       </c>
       <c r="G389" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H389" s="7">
         <v>16</v>
@@ -13020,13 +12612,13 @@
         <v>14800</v>
       </c>
       <c r="E390" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F390" s="6">
         <v>15000</v>
       </c>
       <c r="G390" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H390" s="6">
         <v>20</v>
@@ -13043,13 +12635,13 @@
         <v>16000</v>
       </c>
       <c r="E391" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F391" s="7">
         <v>21600</v>
       </c>
       <c r="G391" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H391" s="7">
         <v>24</v>
@@ -13066,13 +12658,13 @@
         <v>17200</v>
       </c>
       <c r="E392" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F392" s="6">
         <v>29400</v>
       </c>
       <c r="G392" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H392" s="6">
         <v>28</v>
@@ -13089,13 +12681,13 @@
         <v>18400</v>
       </c>
       <c r="E393" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F393" s="7">
         <v>38400</v>
       </c>
       <c r="G393" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H393" s="7">
         <v>32</v>
@@ -13112,13 +12704,13 @@
         <v>19600</v>
       </c>
       <c r="E394" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F394" s="6">
         <v>48600</v>
       </c>
       <c r="G394" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H394" s="6">
         <v>36</v>
@@ -13135,13 +12727,13 @@
         <v>20800</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F395" s="7">
         <v>60000</v>
       </c>
       <c r="G395" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H395" s="7">
         <v>40</v>
@@ -13158,13 +12750,13 @@
         <v>10000</v>
       </c>
       <c r="E396" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F396" s="6">
         <v>600</v>
       </c>
       <c r="G396" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H396" s="6">
         <v>4</v>
@@ -13181,13 +12773,13 @@
         <v>11200</v>
       </c>
       <c r="E397" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F397" s="7">
         <v>2400</v>
       </c>
       <c r="G397" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H397" s="7">
         <v>8</v>
@@ -13204,13 +12796,13 @@
         <v>12400</v>
       </c>
       <c r="E398" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F398" s="6">
         <v>5400</v>
       </c>
       <c r="G398" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H398" s="6">
         <v>12</v>
@@ -13227,13 +12819,13 @@
         <v>13600</v>
       </c>
       <c r="E399" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F399" s="7">
         <v>9600</v>
       </c>
       <c r="G399" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H399" s="7">
         <v>16</v>
@@ -13250,13 +12842,13 @@
         <v>14800</v>
       </c>
       <c r="E400" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F400" s="6">
         <v>15000</v>
       </c>
       <c r="G400" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H400" s="6">
         <v>20</v>
@@ -13273,13 +12865,13 @@
         <v>16000</v>
       </c>
       <c r="E401" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F401" s="7">
         <v>21600</v>
       </c>
       <c r="G401" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H401" s="7">
         <v>24</v>
@@ -13296,13 +12888,13 @@
         <v>17200</v>
       </c>
       <c r="E402" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F402" s="6">
         <v>29400</v>
       </c>
       <c r="G402" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H402" s="6">
         <v>28</v>
@@ -13319,13 +12911,13 @@
         <v>18400</v>
       </c>
       <c r="E403" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F403" s="7">
         <v>38400</v>
       </c>
       <c r="G403" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H403" s="7">
         <v>32</v>
@@ -13342,13 +12934,13 @@
         <v>19600</v>
       </c>
       <c r="E404" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F404" s="6">
         <v>48600</v>
       </c>
       <c r="G404" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H404" s="6">
         <v>36</v>
@@ -13365,13 +12957,13 @@
         <v>20800</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F405" s="7">
         <v>60000</v>
       </c>
       <c r="G405" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H405" s="7">
         <v>40</v>
@@ -13388,13 +12980,13 @@
         <v>10000</v>
       </c>
       <c r="E406" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F406" s="6">
         <v>600</v>
       </c>
       <c r="G406" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H406" s="6">
         <v>4</v>
@@ -13411,13 +13003,13 @@
         <v>11200</v>
       </c>
       <c r="E407" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F407" s="7">
         <v>2400</v>
       </c>
       <c r="G407" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H407" s="7">
         <v>8</v>
@@ -13434,13 +13026,13 @@
         <v>12400</v>
       </c>
       <c r="E408" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F408" s="6">
         <v>5400</v>
       </c>
       <c r="G408" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H408" s="6">
         <v>12</v>
@@ -13457,13 +13049,13 @@
         <v>13600</v>
       </c>
       <c r="E409" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F409" s="7">
         <v>9600</v>
       </c>
       <c r="G409" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H409" s="7">
         <v>16</v>
@@ -13480,13 +13072,13 @@
         <v>14800</v>
       </c>
       <c r="E410" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F410" s="6">
         <v>15000</v>
       </c>
       <c r="G410" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H410" s="6">
         <v>20</v>
@@ -13503,13 +13095,13 @@
         <v>16000</v>
       </c>
       <c r="E411" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F411" s="7">
         <v>21600</v>
       </c>
       <c r="G411" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H411" s="7">
         <v>24</v>
@@ -13526,13 +13118,13 @@
         <v>17200</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F412" s="6">
         <v>29400</v>
       </c>
       <c r="G412" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H412" s="6">
         <v>28</v>
@@ -13549,13 +13141,13 @@
         <v>18400</v>
       </c>
       <c r="E413" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F413" s="7">
         <v>38400</v>
       </c>
       <c r="G413" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H413" s="7">
         <v>32</v>
@@ -13572,13 +13164,13 @@
         <v>19600</v>
       </c>
       <c r="E414" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F414" s="6">
         <v>48600</v>
       </c>
       <c r="G414" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H414" s="6">
         <v>36</v>
@@ -13595,13 +13187,13 @@
         <v>20800</v>
       </c>
       <c r="E415" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F415" s="7">
         <v>60000</v>
       </c>
       <c r="G415" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H415" s="7">
         <v>40</v>
@@ -13618,13 +13210,13 @@
         <v>10000</v>
       </c>
       <c r="E416" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F416" s="6">
         <v>600</v>
       </c>
       <c r="G416" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H416" s="6">
         <v>4</v>
@@ -13641,13 +13233,13 @@
         <v>11200</v>
       </c>
       <c r="E417" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F417" s="7">
         <v>2400</v>
       </c>
       <c r="G417" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H417" s="7">
         <v>8</v>
@@ -13664,13 +13256,13 @@
         <v>12400</v>
       </c>
       <c r="E418" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F418" s="6">
         <v>5400</v>
       </c>
       <c r="G418" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H418" s="6">
         <v>12</v>
@@ -13687,13 +13279,13 @@
         <v>13600</v>
       </c>
       <c r="E419" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F419" s="7">
         <v>9600</v>
       </c>
       <c r="G419" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H419" s="7">
         <v>16</v>
@@ -13710,13 +13302,13 @@
         <v>14800</v>
       </c>
       <c r="E420" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F420" s="6">
         <v>15000</v>
       </c>
       <c r="G420" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H420" s="6">
         <v>20</v>
@@ -13733,13 +13325,13 @@
         <v>16000</v>
       </c>
       <c r="E421" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F421" s="7">
         <v>21600</v>
       </c>
       <c r="G421" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H421" s="7">
         <v>24</v>
@@ -13756,13 +13348,13 @@
         <v>17200</v>
       </c>
       <c r="E422" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F422" s="6">
         <v>29400</v>
       </c>
       <c r="G422" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H422" s="6">
         <v>28</v>
@@ -13779,13 +13371,13 @@
         <v>18400</v>
       </c>
       <c r="E423" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F423" s="7">
         <v>38400</v>
       </c>
       <c r="G423" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H423" s="7">
         <v>32</v>
@@ -13802,13 +13394,13 @@
         <v>19600</v>
       </c>
       <c r="E424" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F424" s="6">
         <v>48600</v>
       </c>
       <c r="G424" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H424" s="6">
         <v>36</v>
@@ -13825,13 +13417,13 @@
         <v>20800</v>
       </c>
       <c r="E425" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F425" s="7">
         <v>60000</v>
       </c>
       <c r="G425" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H425" s="7">
         <v>40</v>
@@ -13848,13 +13440,13 @@
         <v>10000</v>
       </c>
       <c r="E426" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F426" s="6">
         <v>600</v>
       </c>
       <c r="G426" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H426" s="6">
         <v>4</v>
@@ -13871,13 +13463,13 @@
         <v>11200</v>
       </c>
       <c r="E427" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F427" s="7">
         <v>2400</v>
       </c>
       <c r="G427" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H427" s="7">
         <v>8</v>
@@ -13894,13 +13486,13 @@
         <v>12400</v>
       </c>
       <c r="E428" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F428" s="6">
         <v>5400</v>
       </c>
       <c r="G428" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H428" s="6">
         <v>12</v>
@@ -13917,13 +13509,13 @@
         <v>13600</v>
       </c>
       <c r="E429" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F429" s="7">
         <v>9600</v>
       </c>
       <c r="G429" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H429" s="7">
         <v>16</v>
@@ -13940,13 +13532,13 @@
         <v>14800</v>
       </c>
       <c r="E430" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F430" s="6">
         <v>15000</v>
       </c>
       <c r="G430" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H430" s="6">
         <v>20</v>
@@ -13963,13 +13555,13 @@
         <v>16000</v>
       </c>
       <c r="E431" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F431" s="7">
         <v>21600</v>
       </c>
       <c r="G431" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H431" s="7">
         <v>24</v>
@@ -13986,13 +13578,13 @@
         <v>17200</v>
       </c>
       <c r="E432" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F432" s="6">
         <v>29400</v>
       </c>
       <c r="G432" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H432" s="6">
         <v>28</v>
@@ -14009,13 +13601,13 @@
         <v>18400</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F433" s="7">
         <v>38400</v>
       </c>
       <c r="G433" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H433" s="7">
         <v>32</v>
@@ -14032,13 +13624,13 @@
         <v>19600</v>
       </c>
       <c r="E434" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F434" s="6">
         <v>48600</v>
       </c>
       <c r="G434" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H434" s="6">
         <v>36</v>
@@ -14055,13 +13647,13 @@
         <v>20800</v>
       </c>
       <c r="E435" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F435" s="7">
         <v>60000</v>
       </c>
       <c r="G435" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H435" s="7">
         <v>40</v>
@@ -14078,13 +13670,13 @@
         <v>10000</v>
       </c>
       <c r="E436" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F436" s="6">
         <v>600</v>
       </c>
       <c r="G436" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H436" s="6">
         <v>4</v>
@@ -14101,13 +13693,13 @@
         <v>11200</v>
       </c>
       <c r="E437" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F437" s="7">
         <v>2400</v>
       </c>
       <c r="G437" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H437" s="7">
         <v>8</v>
@@ -14124,13 +13716,13 @@
         <v>12400</v>
       </c>
       <c r="E438" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F438" s="6">
         <v>5400</v>
       </c>
       <c r="G438" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H438" s="6">
         <v>12</v>
@@ -14147,13 +13739,13 @@
         <v>13600</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F439" s="7">
         <v>9600</v>
       </c>
       <c r="G439" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H439" s="7">
         <v>16</v>
@@ -14170,13 +13762,13 @@
         <v>14800</v>
       </c>
       <c r="E440" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F440" s="6">
         <v>15000</v>
       </c>
       <c r="G440" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H440" s="6">
         <v>20</v>
@@ -14193,13 +13785,13 @@
         <v>16000</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F441" s="7">
         <v>21600</v>
       </c>
       <c r="G441" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H441" s="7">
         <v>24</v>
@@ -14216,13 +13808,13 @@
         <v>17200</v>
       </c>
       <c r="E442" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F442" s="6">
         <v>29400</v>
       </c>
       <c r="G442" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H442" s="6">
         <v>28</v>
@@ -14239,13 +13831,13 @@
         <v>18400</v>
       </c>
       <c r="E443" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F443" s="7">
         <v>38400</v>
       </c>
       <c r="G443" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H443" s="7">
         <v>32</v>
@@ -14262,13 +13854,13 @@
         <v>19600</v>
       </c>
       <c r="E444" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F444" s="6">
         <v>48600</v>
       </c>
       <c r="G444" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H444" s="6">
         <v>36</v>
@@ -14285,13 +13877,13 @@
         <v>20800</v>
       </c>
       <c r="E445" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F445" s="7">
         <v>60000</v>
       </c>
       <c r="G445" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H445" s="7">
         <v>40</v>
@@ -14308,13 +13900,13 @@
         <v>10000</v>
       </c>
       <c r="E446" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F446" s="6">
         <v>600</v>
       </c>
       <c r="G446" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H446" s="6">
         <v>4</v>
@@ -14331,13 +13923,13 @@
         <v>11200</v>
       </c>
       <c r="E447" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F447" s="7">
         <v>2400</v>
       </c>
       <c r="G447" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H447" s="7">
         <v>8</v>
@@ -14354,13 +13946,13 @@
         <v>12400</v>
       </c>
       <c r="E448" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F448" s="6">
         <v>5400</v>
       </c>
       <c r="G448" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H448" s="6">
         <v>12</v>
@@ -14377,13 +13969,13 @@
         <v>13600</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F449" s="7">
         <v>9600</v>
       </c>
       <c r="G449" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H449" s="7">
         <v>16</v>
@@ -14400,13 +13992,13 @@
         <v>14800</v>
       </c>
       <c r="E450" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F450" s="6">
         <v>15000</v>
       </c>
       <c r="G450" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H450" s="6">
         <v>20</v>
@@ -14423,13 +14015,13 @@
         <v>16000</v>
       </c>
       <c r="E451" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F451" s="7">
         <v>21600</v>
       </c>
       <c r="G451" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H451" s="7">
         <v>24</v>
@@ -14446,13 +14038,13 @@
         <v>17200</v>
       </c>
       <c r="E452" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F452" s="6">
         <v>29400</v>
       </c>
       <c r="G452" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H452" s="6">
         <v>28</v>
@@ -14469,13 +14061,13 @@
         <v>18400</v>
       </c>
       <c r="E453" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F453" s="7">
         <v>38400</v>
       </c>
       <c r="G453" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H453" s="7">
         <v>32</v>
@@ -14492,13 +14084,13 @@
         <v>19600</v>
       </c>
       <c r="E454" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F454" s="6">
         <v>48600</v>
       </c>
       <c r="G454" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H454" s="6">
         <v>36</v>
@@ -14515,13 +14107,13 @@
         <v>20800</v>
       </c>
       <c r="E455" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F455" s="7">
         <v>60000</v>
       </c>
       <c r="G455" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H455" s="7">
         <v>40</v>
@@ -14538,13 +14130,13 @@
         <v>10000</v>
       </c>
       <c r="E456" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F456" s="6">
         <v>600</v>
       </c>
       <c r="G456" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H456" s="6">
         <v>4</v>
@@ -14561,13 +14153,13 @@
         <v>11200</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F457" s="7">
         <v>2400</v>
       </c>
       <c r="G457" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H457" s="7">
         <v>8</v>
@@ -14584,13 +14176,13 @@
         <v>12400</v>
       </c>
       <c r="E458" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F458" s="6">
         <v>5400</v>
       </c>
       <c r="G458" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H458" s="6">
         <v>12</v>
@@ -14607,13 +14199,13 @@
         <v>13600</v>
       </c>
       <c r="E459" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F459" s="7">
         <v>9600</v>
       </c>
       <c r="G459" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H459" s="7">
         <v>16</v>
@@ -14630,13 +14222,13 @@
         <v>14800</v>
       </c>
       <c r="E460" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F460" s="6">
         <v>15000</v>
       </c>
       <c r="G460" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H460" s="6">
         <v>20</v>
@@ -14653,13 +14245,13 @@
         <v>16000</v>
       </c>
       <c r="E461" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F461" s="7">
         <v>21600</v>
       </c>
       <c r="G461" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H461" s="7">
         <v>24</v>
@@ -14676,13 +14268,13 @@
         <v>17200</v>
       </c>
       <c r="E462" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F462" s="6">
         <v>29400</v>
       </c>
       <c r="G462" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H462" s="6">
         <v>28</v>
@@ -14699,13 +14291,13 @@
         <v>18400</v>
       </c>
       <c r="E463" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F463" s="7">
         <v>38400</v>
       </c>
       <c r="G463" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H463" s="7">
         <v>32</v>
@@ -14722,13 +14314,13 @@
         <v>19600</v>
       </c>
       <c r="E464" s="6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F464" s="6">
         <v>48600</v>
       </c>
       <c r="G464" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H464" s="6">
         <v>36</v>
@@ -14745,13 +14337,13 @@
         <v>20800</v>
       </c>
       <c r="E465" s="7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F465" s="7">
         <v>60000</v>
       </c>
       <c r="G465" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H465" s="7">
         <v>40</v>
@@ -14777,10 +14369,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -14791,13 +14383,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>10</v>
@@ -14808,13 +14400,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -14823,13 +14415,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -14870,7 +14462,7 @@
         <v>7500</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -14884,7 +14476,7 @@
         <v>13500</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
@@ -14920,7 +14512,7 @@
         <v>13500</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
@@ -14945,7 +14537,7 @@
         <v>7500</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14">
@@ -14981,7 +14573,7 @@
         <v>7500</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17">
@@ -14995,7 +14587,7 @@
         <v>13500</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18">
@@ -15053,7 +14645,7 @@
         <v>13500</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23">
@@ -15067,7 +14659,7 @@
         <v>13500</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24">
@@ -15092,7 +14684,7 @@
         <v>7500</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26">
@@ -15139,7 +14731,7 @@
         <v>13500</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30">
@@ -15188,10 +14780,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -15225,85 +14817,85 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3">
@@ -15314,10 +14906,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -15325,10 +14917,10 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -15339,10 +14931,10 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="V3" s="4" t="s">
         <v>196</v>
@@ -15362,45 +14954,83 @@
         <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+        <v>283</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>288</v>
+      </c>
       <c r="J4" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+        <v>290</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>298</v>
+      </c>
       <c r="T4" s="4" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
+        <v>301</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -15415,25 +15045,51 @@
       <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="J5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
+      <c r="L5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="T5" s="4" t="s">
         <v>28</v>
       </c>
@@ -15443,19 +15099,31 @@
       <c r="V5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
+      <c r="W5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="D6" s="6">
         <v>18000</v>
@@ -15476,7 +15144,7 @@
         <v>10000</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
@@ -15506,13 +15174,13 @@
         <v>1</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="W6" s="6">
         <v>10000</v>
@@ -15520,28 +15188,16 @@
       <c r="X6" s="6">
         <v>22000</v>
       </c>
-      <c r="Y6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="7">
       <c r="V7" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="W7" s="7">
         <v>3500</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AB7" s="7">
         <v>1</v>
@@ -15549,10 +15205,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="D8" s="6">
         <v>20000</v>
@@ -15573,7 +15229,7 @@
         <v>10000</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
@@ -15606,10 +15262,10 @@
         <v>178</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="W8" s="6">
         <v>10000</v>
@@ -15617,28 +15273,16 @@
       <c r="X8" s="6">
         <v>24000</v>
       </c>
-      <c r="Y8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB8" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="9">
       <c r="V9" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="W9" s="7">
         <v>3500</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AB9" s="7">
         <v>1</v>
@@ -15646,10 +15290,10 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="D10" s="6">
         <v>22000</v>
@@ -15670,7 +15314,7 @@
         <v>10000</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="K10" s="6">
         <v>0</v>
@@ -15700,13 +15344,13 @@
         <v>1</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="W10" s="6">
         <v>10000</v>
@@ -15714,28 +15358,16 @@
       <c r="X10" s="6">
         <v>26000</v>
       </c>
-      <c r="Y10" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA10" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB10" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="11">
       <c r="V11" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="W11" s="7">
         <v>3500</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AB11" s="7">
         <v>1</v>
@@ -15743,10 +15375,10 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="D12" s="6">
         <v>24000</v>
@@ -15767,7 +15399,7 @@
         <v>10000</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="K12" s="6">
         <v>0</v>
@@ -15800,10 +15432,10 @@
         <v>178</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="W12" s="6">
         <v>10000</v>
@@ -15811,28 +15443,16 @@
       <c r="X12" s="6">
         <v>28000</v>
       </c>
-      <c r="Y12" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA12" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB12" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="13">
       <c r="V13" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="W13" s="7">
         <v>3500</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AB13" s="7">
         <v>1</v>
@@ -15840,10 +15460,10 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="D14" s="6">
         <v>26000</v>
@@ -15864,7 +15484,7 @@
         <v>10000</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="K14" s="6">
         <v>0</v>
@@ -15894,13 +15514,13 @@
         <v>1</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="W14" s="6">
         <v>10000</v>
@@ -15908,28 +15528,16 @@
       <c r="X14" s="6">
         <v>30000</v>
       </c>
-      <c r="Y14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA14" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB14" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="15">
       <c r="V15" s="7" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="W15" s="7">
         <v>3500</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AB15" s="7">
         <v>1</v>
